--- a/mapa_classe_sondagens.xlsx
+++ b/mapa_classe_sondagens.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1272,7 +1272,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2304,7 +2304,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2648,7 +2648,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2820,7 +2820,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2863,7 +2863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2906,7 +2906,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3164,7 +3164,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3508,7 +3508,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3594,7 +3594,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4239,7 +4239,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4626,7 +4626,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4712,7 +4712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4884,7 +4884,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5357,7 +5357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5572,7 +5572,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6217,7 +6217,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6303,7 +6303,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6389,7 +6389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6432,7 +6432,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6647,7 +6647,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6690,7 +6690,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6776,7 +6776,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6905,7 +6905,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7034,7 +7034,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7335,7 +7335,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7378,7 +7378,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7507,7 +7507,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7636,7 +7636,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7722,7 +7722,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7765,7 +7765,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7851,7 +7851,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7894,7 +7894,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7937,7 +7937,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8023,7 +8023,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8066,7 +8066,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8152,7 +8152,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8238,7 +8238,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8281,7 +8281,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8324,7 +8324,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8367,7 +8367,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8496,7 +8496,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8539,7 +8539,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8582,7 +8582,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8625,7 +8625,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8668,7 +8668,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8797,7 +8797,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8840,7 +8840,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8883,7 +8883,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8926,7 +8926,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9012,7 +9012,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9055,7 +9055,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>[TESTE] Gerado em: 12/09/2026 12:42 (UTC)</t>
+          <t>[TESTE] Gerado em: 13/09/2026 13:42 (UTC)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -37416,7 +37416,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -37479,7 +37479,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -37605,7 +37605,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -37731,7 +37731,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -37857,7 +37857,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -37983,7 +37983,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -38487,7 +38487,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -39180,7 +39180,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -39243,7 +39243,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -39495,7 +39495,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -39747,7 +39747,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -39999,7 +39999,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -40440,7 +40440,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -40629,7 +40629,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -40755,7 +40755,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -41070,7 +41070,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -41259,7 +41259,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -41511,7 +41511,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -41637,7 +41637,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -41763,7 +41763,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -42015,7 +42015,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -42645,7 +42645,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -42897,7 +42897,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -42960,7 +42960,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -43023,7 +43023,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -43401,7 +43401,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -43527,7 +43527,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -43653,7 +43653,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -43716,7 +43716,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -43779,7 +43779,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -43905,7 +43905,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -43968,7 +43968,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -44031,7 +44031,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -44535,7 +44535,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -44850,7 +44850,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -44913,7 +44913,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -45039,7 +45039,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -45291,7 +45291,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -45417,7 +45417,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -45543,7 +45543,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -45606,7 +45606,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -45732,7 +45732,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -45795,7 +45795,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -45984,7 +45984,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -46047,7 +46047,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -46110,7 +46110,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -46236,7 +46236,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -46362,7 +46362,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -46614,7 +46614,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -46677,7 +46677,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -46740,7 +46740,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -46803,7 +46803,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -47055,7 +47055,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -47118,7 +47118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -47244,7 +47244,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -47307,7 +47307,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -47433,7 +47433,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -47496,7 +47496,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -47559,7 +47559,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -47622,7 +47622,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -47811,7 +47811,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -47874,7 +47874,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -47937,7 +47937,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -48000,7 +48000,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -48252,7 +48252,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -48315,7 +48315,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -48378,7 +48378,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -48441,7 +48441,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -48504,7 +48504,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -48567,7 +48567,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -48630,7 +48630,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -48693,7 +48693,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -48756,7 +48756,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -48819,7 +48819,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -48945,7 +48945,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -49134,7 +49134,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -49260,7 +49260,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -49323,7 +49323,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">

--- a/mapa_classe_sondagens.xlsx
+++ b/mapa_classe_sondagens.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1272,7 +1272,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2304,7 +2304,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2648,7 +2648,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2820,7 +2820,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2863,7 +2863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2906,7 +2906,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3164,7 +3164,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3508,7 +3508,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3594,7 +3594,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4239,7 +4239,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4626,7 +4626,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4712,7 +4712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4884,7 +4884,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5357,7 +5357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5572,7 +5572,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6217,7 +6217,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6303,7 +6303,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6389,7 +6389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6432,7 +6432,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6647,7 +6647,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6690,7 +6690,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6776,7 +6776,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6905,7 +6905,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7034,7 +7034,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7335,7 +7335,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7378,7 +7378,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7507,7 +7507,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7636,7 +7636,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7722,7 +7722,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7765,7 +7765,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7851,7 +7851,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7894,7 +7894,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7937,7 +7937,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8023,7 +8023,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8066,7 +8066,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8152,7 +8152,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8238,7 +8238,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8281,7 +8281,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8324,7 +8324,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8367,7 +8367,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8496,7 +8496,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8539,7 +8539,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8582,7 +8582,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8625,7 +8625,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8668,7 +8668,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8797,7 +8797,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8840,7 +8840,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8883,7 +8883,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8926,7 +8926,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9012,7 +9012,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9055,7 +9055,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>[TESTE] Gerado em: 13/09/2026 13:42 (UTC)</t>
+          <t>[TESTE] Gerado em: 14/09/2026 15:44 (UTC)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -37416,7 +37416,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -37479,7 +37479,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -37605,7 +37605,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -37731,7 +37731,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -37857,7 +37857,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -37983,7 +37983,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -38487,7 +38487,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -39180,7 +39180,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -39243,7 +39243,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -39495,7 +39495,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -39747,7 +39747,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -39999,7 +39999,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -40440,7 +40440,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -40629,7 +40629,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -40755,7 +40755,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -41070,7 +41070,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -41259,7 +41259,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -41511,7 +41511,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -41637,7 +41637,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -41763,7 +41763,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -42015,7 +42015,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -42645,7 +42645,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -42897,7 +42897,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -42960,7 +42960,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -43023,7 +43023,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -43401,7 +43401,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -43527,7 +43527,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -43653,7 +43653,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -43716,7 +43716,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -43779,7 +43779,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -43905,7 +43905,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -43968,7 +43968,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -44031,7 +44031,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -44535,7 +44535,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -44850,7 +44850,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -44913,7 +44913,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -45039,7 +45039,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -45291,7 +45291,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -45417,7 +45417,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -45543,7 +45543,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -45606,7 +45606,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -45732,7 +45732,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -45795,7 +45795,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -45984,7 +45984,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -46047,7 +46047,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -46110,7 +46110,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -46236,7 +46236,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -46362,7 +46362,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -46614,7 +46614,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -46677,7 +46677,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -46740,7 +46740,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -46803,7 +46803,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -47055,7 +47055,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -47118,7 +47118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -47244,7 +47244,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -47307,7 +47307,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -47433,7 +47433,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -47496,7 +47496,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -47559,7 +47559,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -47622,7 +47622,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -47811,7 +47811,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -47874,7 +47874,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -47937,7 +47937,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -48000,7 +48000,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -48252,7 +48252,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -48315,7 +48315,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -48378,7 +48378,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -48441,7 +48441,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -48504,7 +48504,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -48567,7 +48567,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -48630,7 +48630,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -48693,7 +48693,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -48756,7 +48756,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -48819,7 +48819,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -48945,7 +48945,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -49134,7 +49134,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -49260,7 +49260,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -49323,7 +49323,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">

--- a/mapa_classe_sondagens.xlsx
+++ b/mapa_classe_sondagens.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1272,7 +1272,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2304,7 +2304,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2648,7 +2648,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2820,7 +2820,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2863,7 +2863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2906,7 +2906,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3164,7 +3164,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3508,7 +3508,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3594,7 +3594,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4239,7 +4239,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4626,7 +4626,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4712,7 +4712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4884,7 +4884,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5357,7 +5357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5572,7 +5572,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6217,7 +6217,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6303,7 +6303,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6389,7 +6389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6432,7 +6432,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6647,7 +6647,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6690,7 +6690,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6776,7 +6776,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6905,7 +6905,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7034,7 +7034,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7335,7 +7335,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7378,7 +7378,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7507,7 +7507,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7636,7 +7636,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7722,7 +7722,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7765,7 +7765,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7851,7 +7851,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7894,7 +7894,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7937,7 +7937,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8023,7 +8023,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8066,7 +8066,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8152,7 +8152,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8238,7 +8238,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8281,7 +8281,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8324,7 +8324,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8367,7 +8367,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8496,7 +8496,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8539,7 +8539,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8582,7 +8582,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8625,7 +8625,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8668,7 +8668,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8797,7 +8797,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8840,7 +8840,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8883,7 +8883,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8926,7 +8926,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9012,7 +9012,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9055,7 +9055,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>[TESTE] Gerado em: 14/09/2026 15:44 (UTC)</t>
+          <t>[TESTE] Gerado em: 15/09/2026 14:12 (UTC)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -37416,7 +37416,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -37479,7 +37479,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -37605,7 +37605,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -37731,7 +37731,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -37857,7 +37857,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -37983,7 +37983,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -38487,7 +38487,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -39180,7 +39180,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -39243,7 +39243,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -39495,7 +39495,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -39747,7 +39747,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -39999,7 +39999,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -40440,7 +40440,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -40629,7 +40629,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -40755,7 +40755,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -41070,7 +41070,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -41259,7 +41259,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -41511,7 +41511,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -41637,7 +41637,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -41763,7 +41763,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -42015,7 +42015,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -42645,7 +42645,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -42897,7 +42897,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -42960,7 +42960,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -43023,7 +43023,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -43401,7 +43401,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -43527,7 +43527,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -43653,7 +43653,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -43716,7 +43716,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -43779,7 +43779,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -43905,7 +43905,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -43968,7 +43968,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -44031,7 +44031,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -44535,7 +44535,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -44850,7 +44850,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -44913,7 +44913,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -45039,7 +45039,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -45291,7 +45291,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -45417,7 +45417,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -45543,7 +45543,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -45606,7 +45606,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -45732,7 +45732,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -45795,7 +45795,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -45984,7 +45984,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -46047,7 +46047,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -46110,7 +46110,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -46236,7 +46236,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -46362,7 +46362,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -46614,7 +46614,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -46677,7 +46677,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -46740,7 +46740,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -46803,7 +46803,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -47055,7 +47055,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -47118,7 +47118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -47244,7 +47244,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -47307,7 +47307,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -47433,7 +47433,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -47496,7 +47496,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -47559,7 +47559,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -47622,7 +47622,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -47811,7 +47811,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -47874,7 +47874,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -47937,7 +47937,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -48000,7 +48000,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -48252,7 +48252,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -48315,7 +48315,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -48378,7 +48378,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -48441,7 +48441,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -48504,7 +48504,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -48567,7 +48567,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -48630,7 +48630,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -48693,7 +48693,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -48756,7 +48756,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -48819,7 +48819,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -48945,7 +48945,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -49134,7 +49134,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -49260,7 +49260,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -49323,7 +49323,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">

--- a/mapa_classe_sondagens.xlsx
+++ b/mapa_classe_sondagens.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1272,7 +1272,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2304,7 +2304,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2648,7 +2648,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2820,7 +2820,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2863,7 +2863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2906,7 +2906,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3164,7 +3164,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3508,7 +3508,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3594,7 +3594,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4239,7 +4239,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4626,7 +4626,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4712,7 +4712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4884,7 +4884,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5357,7 +5357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5572,7 +5572,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6217,7 +6217,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6303,7 +6303,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6389,7 +6389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6432,7 +6432,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6647,7 +6647,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6690,7 +6690,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6776,7 +6776,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6905,7 +6905,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7034,7 +7034,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7335,7 +7335,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7378,7 +7378,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7507,7 +7507,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7636,7 +7636,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7722,7 +7722,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7765,7 +7765,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7851,7 +7851,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7894,7 +7894,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7937,7 +7937,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8023,7 +8023,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8066,7 +8066,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8152,7 +8152,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8238,7 +8238,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8281,7 +8281,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8324,7 +8324,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8367,7 +8367,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8496,7 +8496,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8539,7 +8539,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8582,7 +8582,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8625,7 +8625,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8668,7 +8668,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8797,7 +8797,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8840,7 +8840,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8883,7 +8883,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8926,7 +8926,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9012,7 +9012,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9055,7 +9055,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>[TESTE] Gerado em: 15/09/2026 14:12 (UTC)</t>
+          <t>[TESTE] Gerado em: 16/09/2026 14:04 (UTC)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -37416,7 +37416,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -37479,7 +37479,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -37605,7 +37605,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -37731,7 +37731,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -37857,7 +37857,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -37983,7 +37983,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -38487,7 +38487,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -39180,7 +39180,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -39243,7 +39243,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -39495,7 +39495,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -39747,7 +39747,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -39999,7 +39999,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -40440,7 +40440,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -40629,7 +40629,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -40755,7 +40755,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -41070,7 +41070,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -41259,7 +41259,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -41511,7 +41511,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -41637,7 +41637,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -41763,7 +41763,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -42015,7 +42015,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -42645,7 +42645,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -42897,7 +42897,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -42960,7 +42960,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -43023,7 +43023,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -43401,7 +43401,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -43527,7 +43527,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -43653,7 +43653,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -43716,7 +43716,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -43779,7 +43779,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -43905,7 +43905,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -43968,7 +43968,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -44031,7 +44031,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -44535,7 +44535,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -44850,7 +44850,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -44913,7 +44913,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -45039,7 +45039,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -45291,7 +45291,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -45417,7 +45417,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -45543,7 +45543,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -45606,7 +45606,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -45732,7 +45732,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -45795,7 +45795,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -45984,7 +45984,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -46047,7 +46047,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -46110,7 +46110,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -46236,7 +46236,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -46362,7 +46362,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -46614,7 +46614,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -46677,7 +46677,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -46740,7 +46740,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -46803,7 +46803,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -47055,7 +47055,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -47118,7 +47118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -47244,7 +47244,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -47307,7 +47307,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -47433,7 +47433,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -47496,7 +47496,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -47559,7 +47559,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -47622,7 +47622,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -47811,7 +47811,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -47874,7 +47874,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -47937,7 +47937,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -48000,7 +48000,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -48252,7 +48252,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -48315,7 +48315,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -48378,7 +48378,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -48441,7 +48441,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -48504,7 +48504,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -48567,7 +48567,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -48630,7 +48630,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -48693,7 +48693,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -48756,7 +48756,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -48819,7 +48819,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -48945,7 +48945,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -49134,7 +49134,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -49260,7 +49260,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -49323,7 +49323,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">

--- a/mapa_classe_sondagens.xlsx
+++ b/mapa_classe_sondagens.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1272,7 +1272,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2304,7 +2304,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2648,7 +2648,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2820,7 +2820,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2863,7 +2863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2906,7 +2906,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3164,7 +3164,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3508,7 +3508,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3594,7 +3594,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4239,7 +4239,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4626,7 +4626,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4712,7 +4712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4884,7 +4884,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5357,7 +5357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5572,7 +5572,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6217,7 +6217,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6303,7 +6303,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6389,7 +6389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6432,7 +6432,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6647,7 +6647,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6690,7 +6690,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6776,7 +6776,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6905,7 +6905,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7034,7 +7034,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7335,7 +7335,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7378,7 +7378,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7507,7 +7507,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7636,7 +7636,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7722,7 +7722,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7765,7 +7765,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7851,7 +7851,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7894,7 +7894,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7937,7 +7937,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8023,7 +8023,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8066,7 +8066,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8152,7 +8152,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8238,7 +8238,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8281,7 +8281,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8324,7 +8324,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8367,7 +8367,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8496,7 +8496,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8539,7 +8539,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8582,7 +8582,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8625,7 +8625,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8668,7 +8668,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8797,7 +8797,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8840,7 +8840,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8883,7 +8883,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8926,7 +8926,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9012,7 +9012,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9055,7 +9055,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>[TESTE] Gerado em: 16/09/2026 14:04 (UTC)</t>
+          <t>[TESTE] Gerado em: 17/09/2026 14:09 (UTC)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -37416,7 +37416,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -37479,7 +37479,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -37605,7 +37605,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -37731,7 +37731,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -37857,7 +37857,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -37983,7 +37983,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -38487,7 +38487,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -39180,7 +39180,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -39243,7 +39243,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -39495,7 +39495,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -39747,7 +39747,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -39999,7 +39999,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -40440,7 +40440,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -40629,7 +40629,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -40755,7 +40755,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -41070,7 +41070,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -41259,7 +41259,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -41511,7 +41511,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -41637,7 +41637,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -41763,7 +41763,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -42015,7 +42015,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -42645,7 +42645,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -42897,7 +42897,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -42960,7 +42960,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -43023,7 +43023,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -43401,7 +43401,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -43527,7 +43527,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -43653,7 +43653,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -43716,7 +43716,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -43779,7 +43779,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -43905,7 +43905,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -43968,7 +43968,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -44031,7 +44031,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -44535,7 +44535,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -44850,7 +44850,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -44913,7 +44913,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -45039,7 +45039,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -45291,7 +45291,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -45417,7 +45417,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -45543,7 +45543,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -45606,7 +45606,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -45732,7 +45732,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -45795,7 +45795,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -45984,7 +45984,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -46047,7 +46047,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -46110,7 +46110,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -46236,7 +46236,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -46362,7 +46362,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -46614,7 +46614,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -46677,7 +46677,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -46740,7 +46740,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -46803,7 +46803,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -47055,7 +47055,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -47118,7 +47118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -47244,7 +47244,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -47307,7 +47307,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -47433,7 +47433,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -47496,7 +47496,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -47559,7 +47559,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -47622,7 +47622,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -47811,7 +47811,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -47874,7 +47874,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -47937,7 +47937,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -48000,7 +48000,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -48252,7 +48252,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -48315,7 +48315,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -48378,7 +48378,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -48441,7 +48441,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -48504,7 +48504,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -48567,7 +48567,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -48630,7 +48630,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -48693,7 +48693,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -48756,7 +48756,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -48819,7 +48819,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -48945,7 +48945,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -49134,7 +49134,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -49260,7 +49260,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -49323,7 +49323,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">

--- a/mapa_classe_sondagens.xlsx
+++ b/mapa_classe_sondagens.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1272,7 +1272,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2304,7 +2304,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2648,7 +2648,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2820,7 +2820,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2863,7 +2863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2906,7 +2906,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3164,7 +3164,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3508,7 +3508,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3594,7 +3594,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4239,7 +4239,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4626,7 +4626,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4712,7 +4712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4884,7 +4884,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5357,7 +5357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5572,7 +5572,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6217,7 +6217,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6303,7 +6303,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6389,7 +6389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6432,7 +6432,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6647,7 +6647,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6690,7 +6690,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6776,7 +6776,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6905,7 +6905,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7034,7 +7034,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7335,7 +7335,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7378,7 +7378,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7507,7 +7507,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7636,7 +7636,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7722,7 +7722,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7765,7 +7765,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7851,7 +7851,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7894,7 +7894,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7937,7 +7937,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8023,7 +8023,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8066,7 +8066,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8152,7 +8152,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8238,7 +8238,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8281,7 +8281,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8324,7 +8324,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8367,7 +8367,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8496,7 +8496,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8539,7 +8539,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8582,7 +8582,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8625,7 +8625,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8668,7 +8668,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8797,7 +8797,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8840,7 +8840,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8883,7 +8883,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8926,7 +8926,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9012,7 +9012,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9055,7 +9055,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>[TESTE] Gerado em: 17/09/2026 14:09 (UTC)</t>
+          <t>[TESTE] Gerado em: 18/09/2026 13:28 (UTC)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -37416,7 +37416,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -37479,7 +37479,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -37605,7 +37605,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -37731,7 +37731,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -37857,7 +37857,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -37983,7 +37983,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -38487,7 +38487,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -39180,7 +39180,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -39243,7 +39243,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -39495,7 +39495,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -39747,7 +39747,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -39999,7 +39999,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -40440,7 +40440,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -40629,7 +40629,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -40755,7 +40755,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -41070,7 +41070,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -41259,7 +41259,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -41511,7 +41511,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -41637,7 +41637,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -41763,7 +41763,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -42015,7 +42015,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -42645,7 +42645,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -42897,7 +42897,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -42960,7 +42960,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -43023,7 +43023,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -43401,7 +43401,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -43527,7 +43527,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -43653,7 +43653,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -43716,7 +43716,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -43779,7 +43779,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -43905,7 +43905,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -43968,7 +43968,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -44031,7 +44031,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -44535,7 +44535,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -44850,7 +44850,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -44913,7 +44913,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -45039,7 +45039,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -45291,7 +45291,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -45417,7 +45417,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -45543,7 +45543,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -45606,7 +45606,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -45732,7 +45732,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -45795,7 +45795,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -45984,7 +45984,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -46047,7 +46047,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -46110,7 +46110,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -46236,7 +46236,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -46362,7 +46362,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -46614,7 +46614,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -46677,7 +46677,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -46740,7 +46740,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -46803,7 +46803,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -47055,7 +47055,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -47118,7 +47118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -47244,7 +47244,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -47307,7 +47307,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -47433,7 +47433,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -47496,7 +47496,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -47559,7 +47559,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -47622,7 +47622,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -47811,7 +47811,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -47874,7 +47874,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -47937,7 +47937,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -48000,7 +48000,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -48252,7 +48252,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -48315,7 +48315,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -48378,7 +48378,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -48441,7 +48441,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -48504,7 +48504,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -48567,7 +48567,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -48630,7 +48630,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -48693,7 +48693,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -48756,7 +48756,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -48819,7 +48819,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -48945,7 +48945,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -49134,7 +49134,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -49260,7 +49260,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -49323,7 +49323,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">

--- a/mapa_classe_sondagens.xlsx
+++ b/mapa_classe_sondagens.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1272,7 +1272,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2304,7 +2304,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2648,7 +2648,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2820,7 +2820,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2863,7 +2863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2906,7 +2906,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3164,7 +3164,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3508,7 +3508,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3594,7 +3594,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4239,7 +4239,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4626,7 +4626,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4712,7 +4712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4884,7 +4884,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5357,7 +5357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5572,7 +5572,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6217,7 +6217,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6303,7 +6303,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6389,7 +6389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6432,7 +6432,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6647,7 +6647,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6690,7 +6690,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6776,7 +6776,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6905,7 +6905,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7034,7 +7034,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7335,7 +7335,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7378,7 +7378,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7507,7 +7507,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7636,7 +7636,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7722,7 +7722,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7765,7 +7765,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7851,7 +7851,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7894,7 +7894,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7937,7 +7937,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8023,7 +8023,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8066,7 +8066,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8152,7 +8152,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8238,7 +8238,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8281,7 +8281,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8324,7 +8324,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8367,7 +8367,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8496,7 +8496,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8539,7 +8539,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8582,7 +8582,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8625,7 +8625,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8668,7 +8668,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8797,7 +8797,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8840,7 +8840,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8883,7 +8883,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8926,7 +8926,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9012,7 +9012,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9055,7 +9055,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>[TESTE] Gerado em: 18/09/2026 13:28 (UTC)</t>
+          <t>[TESTE] Gerado em: 19/09/2026 12:57 (UTC)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -37416,7 +37416,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -37479,7 +37479,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -37605,7 +37605,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -37731,7 +37731,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -37857,7 +37857,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -37983,7 +37983,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -38487,7 +38487,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -39180,7 +39180,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -39243,7 +39243,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -39495,7 +39495,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -39747,7 +39747,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -39999,7 +39999,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -40440,7 +40440,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -40629,7 +40629,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -40755,7 +40755,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -41070,7 +41070,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -41259,7 +41259,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -41511,7 +41511,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -41637,7 +41637,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -41763,7 +41763,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -42015,7 +42015,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -42645,7 +42645,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -42897,7 +42897,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -42960,7 +42960,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -43023,7 +43023,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -43401,7 +43401,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -43527,7 +43527,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -43653,7 +43653,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -43716,7 +43716,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -43779,7 +43779,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -43905,7 +43905,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -43968,7 +43968,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -44031,7 +44031,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -44535,7 +44535,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -44850,7 +44850,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -44913,7 +44913,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -45039,7 +45039,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -45291,7 +45291,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -45417,7 +45417,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -45543,7 +45543,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -45606,7 +45606,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -45732,7 +45732,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -45795,7 +45795,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -45984,7 +45984,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -46047,7 +46047,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -46110,7 +46110,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -46236,7 +46236,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -46362,7 +46362,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -46614,7 +46614,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -46677,7 +46677,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -46740,7 +46740,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -46803,7 +46803,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -47055,7 +47055,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -47118,7 +47118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -47244,7 +47244,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -47307,7 +47307,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -47433,7 +47433,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -47496,7 +47496,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -47559,7 +47559,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -47622,7 +47622,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -47811,7 +47811,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -47874,7 +47874,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -47937,7 +47937,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -48000,7 +48000,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -48252,7 +48252,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -48315,7 +48315,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -48378,7 +48378,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -48441,7 +48441,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -48504,7 +48504,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -48567,7 +48567,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -48630,7 +48630,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -48693,7 +48693,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -48756,7 +48756,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -48819,7 +48819,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -48945,7 +48945,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -49134,7 +49134,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -49260,7 +49260,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -49323,7 +49323,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">

--- a/mapa_classe_sondagens.xlsx
+++ b/mapa_classe_sondagens.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1272,7 +1272,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2304,7 +2304,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2648,7 +2648,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2820,7 +2820,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2863,7 +2863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2906,7 +2906,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3164,7 +3164,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3508,7 +3508,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3594,7 +3594,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4239,7 +4239,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4626,7 +4626,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4712,7 +4712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4884,7 +4884,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5357,7 +5357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5572,7 +5572,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6217,7 +6217,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6303,7 +6303,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6389,7 +6389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6432,7 +6432,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6647,7 +6647,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6690,7 +6690,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6776,7 +6776,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6905,7 +6905,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7034,7 +7034,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7335,7 +7335,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7378,7 +7378,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7507,7 +7507,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7636,7 +7636,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7722,7 +7722,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7765,7 +7765,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7851,7 +7851,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7894,7 +7894,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7937,7 +7937,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8023,7 +8023,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8066,7 +8066,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8152,7 +8152,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8238,7 +8238,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8281,7 +8281,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8324,7 +8324,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8367,7 +8367,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8496,7 +8496,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8539,7 +8539,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8582,7 +8582,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8625,7 +8625,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8668,7 +8668,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8797,7 +8797,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8840,7 +8840,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8883,7 +8883,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8926,7 +8926,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9012,7 +9012,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9055,7 +9055,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>[TESTE] Gerado em: 19/09/2026 12:57 (UTC)</t>
+          <t>[TESTE] Gerado em: 20/09/2026 13:29 (UTC)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -37416,7 +37416,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -37479,7 +37479,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -37605,7 +37605,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -37731,7 +37731,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -37857,7 +37857,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -37983,7 +37983,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -38487,7 +38487,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -39180,7 +39180,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -39243,7 +39243,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -39495,7 +39495,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -39747,7 +39747,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -39999,7 +39999,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -40440,7 +40440,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -40629,7 +40629,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -40755,7 +40755,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -41070,7 +41070,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -41259,7 +41259,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -41511,7 +41511,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -41637,7 +41637,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -41763,7 +41763,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -42015,7 +42015,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -42645,7 +42645,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -42897,7 +42897,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -42960,7 +42960,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -43023,7 +43023,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -43401,7 +43401,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -43527,7 +43527,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -43653,7 +43653,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -43716,7 +43716,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -43779,7 +43779,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -43905,7 +43905,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -43968,7 +43968,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -44031,7 +44031,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -44535,7 +44535,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -44850,7 +44850,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -44913,7 +44913,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -45039,7 +45039,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -45291,7 +45291,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -45417,7 +45417,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -45543,7 +45543,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -45606,7 +45606,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -45732,7 +45732,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -45795,7 +45795,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -45984,7 +45984,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -46047,7 +46047,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -46110,7 +46110,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -46236,7 +46236,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -46362,7 +46362,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -46614,7 +46614,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -46677,7 +46677,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -46740,7 +46740,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -46803,7 +46803,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -47055,7 +47055,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -47118,7 +47118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -47244,7 +47244,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -47307,7 +47307,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -47433,7 +47433,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -47496,7 +47496,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -47559,7 +47559,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -47622,7 +47622,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -47811,7 +47811,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -47874,7 +47874,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -47937,7 +47937,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -48000,7 +48000,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -48252,7 +48252,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -48315,7 +48315,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -48378,7 +48378,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -48441,7 +48441,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -48504,7 +48504,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -48567,7 +48567,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -48630,7 +48630,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -48693,7 +48693,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -48756,7 +48756,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -48819,7 +48819,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -48945,7 +48945,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -49134,7 +49134,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -49260,7 +49260,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -49323,7 +49323,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">

--- a/mapa_classe_sondagens.xlsx
+++ b/mapa_classe_sondagens.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1272,7 +1272,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2304,7 +2304,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2648,7 +2648,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2820,7 +2820,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2863,7 +2863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2906,7 +2906,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3164,7 +3164,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3508,7 +3508,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3594,7 +3594,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4239,7 +4239,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4626,7 +4626,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4712,7 +4712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4884,7 +4884,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5357,7 +5357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5572,7 +5572,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6217,7 +6217,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6303,7 +6303,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6389,7 +6389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6432,7 +6432,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6647,7 +6647,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6690,7 +6690,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6776,7 +6776,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6905,7 +6905,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7034,7 +7034,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7335,7 +7335,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7378,7 +7378,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7507,7 +7507,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7636,7 +7636,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7722,7 +7722,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7765,7 +7765,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7851,7 +7851,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7894,7 +7894,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7937,7 +7937,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8023,7 +8023,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8066,7 +8066,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8152,7 +8152,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8238,7 +8238,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8281,7 +8281,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8324,7 +8324,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8367,7 +8367,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8496,7 +8496,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8539,7 +8539,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8582,7 +8582,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8625,7 +8625,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8668,7 +8668,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8797,7 +8797,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8840,7 +8840,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8883,7 +8883,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8926,7 +8926,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9012,7 +9012,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9055,7 +9055,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>[TESTE] Gerado em: 20/09/2026 13:29 (UTC)</t>
+          <t>[TESTE] Gerado em: 21/09/2026 15:43 (UTC)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -37416,7 +37416,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -37479,7 +37479,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -37605,7 +37605,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -37731,7 +37731,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -37857,7 +37857,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -37983,7 +37983,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -38487,7 +38487,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -39180,7 +39180,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -39243,7 +39243,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -39495,7 +39495,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -39747,7 +39747,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -39999,7 +39999,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -40440,7 +40440,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -40629,7 +40629,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -40755,7 +40755,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -41070,7 +41070,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -41259,7 +41259,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -41511,7 +41511,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -41637,7 +41637,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -41763,7 +41763,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -42015,7 +42015,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -42645,7 +42645,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -42897,7 +42897,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -42960,7 +42960,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -43023,7 +43023,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -43401,7 +43401,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -43527,7 +43527,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -43653,7 +43653,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -43716,7 +43716,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -43779,7 +43779,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -43905,7 +43905,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -43968,7 +43968,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -44031,7 +44031,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -44535,7 +44535,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -44850,7 +44850,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -44913,7 +44913,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -45039,7 +45039,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -45291,7 +45291,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -45417,7 +45417,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -45543,7 +45543,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -45606,7 +45606,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -45732,7 +45732,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -45795,7 +45795,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -45984,7 +45984,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -46047,7 +46047,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -46110,7 +46110,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -46236,7 +46236,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -46362,7 +46362,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -46614,7 +46614,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -46677,7 +46677,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -46740,7 +46740,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -46803,7 +46803,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -47055,7 +47055,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -47118,7 +47118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -47244,7 +47244,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -47307,7 +47307,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -47433,7 +47433,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -47496,7 +47496,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -47559,7 +47559,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -47622,7 +47622,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -47811,7 +47811,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -47874,7 +47874,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -47937,7 +47937,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -48000,7 +48000,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -48252,7 +48252,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -48315,7 +48315,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -48378,7 +48378,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -48441,7 +48441,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -48504,7 +48504,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -48567,7 +48567,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -48630,7 +48630,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -48693,7 +48693,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -48756,7 +48756,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -48819,7 +48819,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -48945,7 +48945,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -49134,7 +49134,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -49260,7 +49260,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -49323,7 +49323,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">

--- a/mapa_classe_sondagens.xlsx
+++ b/mapa_classe_sondagens.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1272,7 +1272,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2304,7 +2304,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2648,7 +2648,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2820,7 +2820,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2863,7 +2863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2906,7 +2906,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3164,7 +3164,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3508,7 +3508,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3594,7 +3594,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4239,7 +4239,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4626,7 +4626,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4712,7 +4712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4884,7 +4884,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5357,7 +5357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5572,7 +5572,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6217,7 +6217,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6303,7 +6303,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6389,7 +6389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6432,7 +6432,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6647,7 +6647,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6690,7 +6690,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6776,7 +6776,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6905,7 +6905,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7034,7 +7034,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7335,7 +7335,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7378,7 +7378,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7507,7 +7507,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7636,7 +7636,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7722,7 +7722,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7765,7 +7765,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7851,7 +7851,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7894,7 +7894,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7937,7 +7937,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8023,7 +8023,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8066,7 +8066,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8152,7 +8152,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8238,7 +8238,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8281,7 +8281,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8324,7 +8324,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8367,7 +8367,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8496,7 +8496,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8539,7 +8539,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8582,7 +8582,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8625,7 +8625,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8668,7 +8668,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8797,7 +8797,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8840,7 +8840,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8883,7 +8883,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8926,7 +8926,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9012,7 +9012,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9055,7 +9055,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>[TESTE] Gerado em: 21/09/2026 15:43 (UTC)</t>
+          <t>[TESTE] Gerado em: 22/09/2026 13:55 (UTC)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -37416,7 +37416,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -37479,7 +37479,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -37605,7 +37605,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -37731,7 +37731,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -37857,7 +37857,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -37983,7 +37983,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -38487,7 +38487,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -39180,7 +39180,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -39243,7 +39243,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -39495,7 +39495,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -39747,7 +39747,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -39999,7 +39999,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -40440,7 +40440,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -40629,7 +40629,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -40755,7 +40755,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -41070,7 +41070,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -41259,7 +41259,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -41511,7 +41511,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -41637,7 +41637,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -41763,7 +41763,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -42015,7 +42015,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -42645,7 +42645,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -42897,7 +42897,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -42960,7 +42960,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -43023,7 +43023,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -43401,7 +43401,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -43527,7 +43527,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -43653,7 +43653,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -43716,7 +43716,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -43779,7 +43779,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -43905,7 +43905,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -43968,7 +43968,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -44031,7 +44031,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -44535,7 +44535,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -44850,7 +44850,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -44913,7 +44913,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -45039,7 +45039,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -45291,7 +45291,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -45417,7 +45417,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -45543,7 +45543,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -45606,7 +45606,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -45732,7 +45732,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -45795,7 +45795,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -45984,7 +45984,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -46047,7 +46047,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -46110,7 +46110,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -46236,7 +46236,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -46362,7 +46362,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -46614,7 +46614,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -46677,7 +46677,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -46740,7 +46740,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -46803,7 +46803,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -47055,7 +47055,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -47118,7 +47118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -47244,7 +47244,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -47307,7 +47307,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -47433,7 +47433,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -47496,7 +47496,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -47559,7 +47559,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -47622,7 +47622,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -47811,7 +47811,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -47874,7 +47874,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -47937,7 +47937,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -48000,7 +48000,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -48252,7 +48252,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -48315,7 +48315,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -48378,7 +48378,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -48441,7 +48441,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -48504,7 +48504,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -48567,7 +48567,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -48630,7 +48630,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -48693,7 +48693,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -48756,7 +48756,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -48819,7 +48819,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -48945,7 +48945,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -49134,7 +49134,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -49260,7 +49260,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -49323,7 +49323,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">

--- a/mapa_classe_sondagens.xlsx
+++ b/mapa_classe_sondagens.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1272,7 +1272,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2304,7 +2304,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2648,7 +2648,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2820,7 +2820,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2863,7 +2863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2906,7 +2906,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3164,7 +3164,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3508,7 +3508,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3594,7 +3594,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4239,7 +4239,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4626,7 +4626,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4712,7 +4712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4884,7 +4884,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5357,7 +5357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5572,7 +5572,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6217,7 +6217,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6303,7 +6303,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6389,7 +6389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6432,7 +6432,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6647,7 +6647,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6690,7 +6690,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6776,7 +6776,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6905,7 +6905,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7034,7 +7034,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7335,7 +7335,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7378,7 +7378,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7507,7 +7507,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7636,7 +7636,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7722,7 +7722,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7765,7 +7765,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7851,7 +7851,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7894,7 +7894,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7937,7 +7937,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8023,7 +8023,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8066,7 +8066,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8152,7 +8152,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8238,7 +8238,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8281,7 +8281,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8324,7 +8324,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8367,7 +8367,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8496,7 +8496,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8539,7 +8539,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8582,7 +8582,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8625,7 +8625,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8668,7 +8668,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8797,7 +8797,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8840,7 +8840,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8883,7 +8883,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8926,7 +8926,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9012,7 +9012,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9055,7 +9055,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>[TESTE] Gerado em: 22/09/2026 13:55 (UTC)</t>
+          <t>[TESTE] Gerado em: 23/09/2026 14:06 (UTC)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -37416,7 +37416,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -37479,7 +37479,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -37605,7 +37605,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -37731,7 +37731,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -37857,7 +37857,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -37983,7 +37983,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -38487,7 +38487,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -39180,7 +39180,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -39243,7 +39243,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -39495,7 +39495,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -39747,7 +39747,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -39999,7 +39999,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -40440,7 +40440,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -40629,7 +40629,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -40755,7 +40755,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -41070,7 +41070,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -41259,7 +41259,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -41511,7 +41511,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -41637,7 +41637,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -41763,7 +41763,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -42015,7 +42015,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -42645,7 +42645,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -42897,7 +42897,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -42960,7 +42960,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -43023,7 +43023,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -43401,7 +43401,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -43527,7 +43527,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -43653,7 +43653,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -43716,7 +43716,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -43779,7 +43779,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -43905,7 +43905,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -43968,7 +43968,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -44031,7 +44031,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -44535,7 +44535,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -44850,7 +44850,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -44913,7 +44913,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -45039,7 +45039,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -45291,7 +45291,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -45417,7 +45417,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -45543,7 +45543,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -45606,7 +45606,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -45732,7 +45732,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -45795,7 +45795,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -45984,7 +45984,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -46047,7 +46047,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -46110,7 +46110,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -46236,7 +46236,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -46362,7 +46362,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -46614,7 +46614,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -46677,7 +46677,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -46740,7 +46740,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -46803,7 +46803,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -47055,7 +47055,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -47118,7 +47118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -47244,7 +47244,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -47307,7 +47307,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -47433,7 +47433,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -47496,7 +47496,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -47559,7 +47559,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -47622,7 +47622,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -47811,7 +47811,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -47874,7 +47874,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -47937,7 +47937,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -48000,7 +48000,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -48252,7 +48252,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -48315,7 +48315,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -48378,7 +48378,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -48441,7 +48441,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -48504,7 +48504,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -48567,7 +48567,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -48630,7 +48630,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -48693,7 +48693,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -48756,7 +48756,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -48819,7 +48819,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -48945,7 +48945,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -49134,7 +49134,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -49260,7 +49260,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -49323,7 +49323,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">

--- a/mapa_classe_sondagens.xlsx
+++ b/mapa_classe_sondagens.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1272,7 +1272,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2304,7 +2304,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2648,7 +2648,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2820,7 +2820,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2863,7 +2863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2906,7 +2906,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3164,7 +3164,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3508,7 +3508,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3594,7 +3594,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4239,7 +4239,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4626,7 +4626,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4712,7 +4712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4884,7 +4884,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5357,7 +5357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5572,7 +5572,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6217,7 +6217,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6303,7 +6303,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6389,7 +6389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6432,7 +6432,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6647,7 +6647,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6690,7 +6690,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6776,7 +6776,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6905,7 +6905,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7034,7 +7034,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7335,7 +7335,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7378,7 +7378,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7507,7 +7507,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7636,7 +7636,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7722,7 +7722,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7765,7 +7765,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7851,7 +7851,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7894,7 +7894,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7937,7 +7937,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8023,7 +8023,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8066,7 +8066,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8152,7 +8152,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8238,7 +8238,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8281,7 +8281,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8324,7 +8324,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8367,7 +8367,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8496,7 +8496,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8539,7 +8539,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8582,7 +8582,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8625,7 +8625,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8668,7 +8668,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8797,7 +8797,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8840,7 +8840,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8883,7 +8883,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8926,7 +8926,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9012,7 +9012,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9055,7 +9055,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>[TESTE] Gerado em: 23/09/2026 14:06 (UTC)</t>
+          <t>[TESTE] Gerado em: 24/09/2026 14:04 (UTC)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -37416,7 +37416,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -37479,7 +37479,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -37605,7 +37605,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -37731,7 +37731,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -37857,7 +37857,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -37983,7 +37983,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -38487,7 +38487,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -39180,7 +39180,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -39243,7 +39243,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -39495,7 +39495,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -39747,7 +39747,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -39999,7 +39999,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -40440,7 +40440,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -40629,7 +40629,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -40755,7 +40755,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -41070,7 +41070,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -41259,7 +41259,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -41511,7 +41511,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -41637,7 +41637,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -41763,7 +41763,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -42015,7 +42015,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -42645,7 +42645,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -42897,7 +42897,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -42960,7 +42960,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -43023,7 +43023,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -43401,7 +43401,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -43527,7 +43527,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -43653,7 +43653,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -43716,7 +43716,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -43779,7 +43779,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -43905,7 +43905,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -43968,7 +43968,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -44031,7 +44031,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -44535,7 +44535,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -44850,7 +44850,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -44913,7 +44913,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -45039,7 +45039,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -45291,7 +45291,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -45417,7 +45417,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -45543,7 +45543,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -45606,7 +45606,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -45732,7 +45732,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -45795,7 +45795,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -45984,7 +45984,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -46047,7 +46047,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -46110,7 +46110,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -46236,7 +46236,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -46362,7 +46362,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -46614,7 +46614,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -46677,7 +46677,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -46740,7 +46740,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -46803,7 +46803,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -47055,7 +47055,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -47118,7 +47118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -47244,7 +47244,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -47307,7 +47307,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -47433,7 +47433,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -47496,7 +47496,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -47559,7 +47559,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -47622,7 +47622,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -47811,7 +47811,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -47874,7 +47874,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -47937,7 +47937,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -48000,7 +48000,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -48252,7 +48252,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -48315,7 +48315,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -48378,7 +48378,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -48441,7 +48441,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -48504,7 +48504,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -48567,7 +48567,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -48630,7 +48630,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -48693,7 +48693,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -48756,7 +48756,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -48819,7 +48819,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -48945,7 +48945,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -49134,7 +49134,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -49260,7 +49260,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -49323,7 +49323,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">

--- a/mapa_classe_sondagens.xlsx
+++ b/mapa_classe_sondagens.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1272,7 +1272,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2304,7 +2304,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2648,7 +2648,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2820,7 +2820,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2863,7 +2863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2906,7 +2906,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3164,7 +3164,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3508,7 +3508,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3594,7 +3594,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4239,7 +4239,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4626,7 +4626,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4712,7 +4712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4884,7 +4884,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5357,7 +5357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5572,7 +5572,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6217,7 +6217,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6303,7 +6303,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6389,7 +6389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6432,7 +6432,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6647,7 +6647,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6690,7 +6690,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6776,7 +6776,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6905,7 +6905,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7034,7 +7034,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7335,7 +7335,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7378,7 +7378,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7507,7 +7507,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7636,7 +7636,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7722,7 +7722,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7765,7 +7765,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7851,7 +7851,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7894,7 +7894,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7937,7 +7937,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8023,7 +8023,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8066,7 +8066,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8152,7 +8152,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8238,7 +8238,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8281,7 +8281,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8324,7 +8324,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8367,7 +8367,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8496,7 +8496,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8539,7 +8539,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8582,7 +8582,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8625,7 +8625,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8668,7 +8668,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8797,7 +8797,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8840,7 +8840,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8883,7 +8883,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8926,7 +8926,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9012,7 +9012,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9055,7 +9055,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>[TESTE] Gerado em: 24/09/2026 14:04 (UTC)</t>
+          <t>[TESTE] Gerado em: 25/09/2026 14:28 (UTC)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -37416,7 +37416,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -37479,7 +37479,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -37605,7 +37605,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -37731,7 +37731,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -37857,7 +37857,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -37983,7 +37983,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -38487,7 +38487,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -39180,7 +39180,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -39243,7 +39243,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -39495,7 +39495,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -39747,7 +39747,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -39999,7 +39999,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -40440,7 +40440,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -40629,7 +40629,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -40755,7 +40755,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -41070,7 +41070,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -41259,7 +41259,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -41511,7 +41511,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -41637,7 +41637,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -41763,7 +41763,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -42015,7 +42015,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -42645,7 +42645,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -42897,7 +42897,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -42960,7 +42960,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -43023,7 +43023,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -43401,7 +43401,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -43527,7 +43527,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -43653,7 +43653,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -43716,7 +43716,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -43779,7 +43779,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -43905,7 +43905,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -43968,7 +43968,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -44031,7 +44031,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -44535,7 +44535,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -44850,7 +44850,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -44913,7 +44913,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -45039,7 +45039,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -45291,7 +45291,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -45417,7 +45417,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -45543,7 +45543,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -45606,7 +45606,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -45732,7 +45732,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -45795,7 +45795,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -45984,7 +45984,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -46047,7 +46047,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -46110,7 +46110,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -46236,7 +46236,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -46362,7 +46362,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -46614,7 +46614,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -46677,7 +46677,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -46740,7 +46740,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -46803,7 +46803,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -47055,7 +47055,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -47118,7 +47118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -47244,7 +47244,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -47307,7 +47307,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -47433,7 +47433,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -47496,7 +47496,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -47559,7 +47559,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -47622,7 +47622,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -47811,7 +47811,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -47874,7 +47874,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -47937,7 +47937,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -48000,7 +48000,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -48252,7 +48252,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -48315,7 +48315,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -48378,7 +48378,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -48441,7 +48441,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -48504,7 +48504,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -48567,7 +48567,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -48630,7 +48630,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -48693,7 +48693,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -48756,7 +48756,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -48819,7 +48819,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -48945,7 +48945,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -49134,7 +49134,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -49260,7 +49260,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -49323,7 +49323,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">

--- a/mapa_classe_sondagens.xlsx
+++ b/mapa_classe_sondagens.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1272,7 +1272,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2304,7 +2304,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2648,7 +2648,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2820,7 +2820,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2863,7 +2863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2906,7 +2906,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3164,7 +3164,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3508,7 +3508,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3594,7 +3594,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4239,7 +4239,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4626,7 +4626,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4712,7 +4712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4884,7 +4884,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5357,7 +5357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5572,7 +5572,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6217,7 +6217,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6303,7 +6303,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6389,7 +6389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6432,7 +6432,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6647,7 +6647,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6690,7 +6690,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6776,7 +6776,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6905,7 +6905,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7034,7 +7034,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7335,7 +7335,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7378,7 +7378,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7507,7 +7507,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7636,7 +7636,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7722,7 +7722,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7765,7 +7765,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7851,7 +7851,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7894,7 +7894,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7937,7 +7937,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8023,7 +8023,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8066,7 +8066,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8152,7 +8152,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8238,7 +8238,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8281,7 +8281,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8324,7 +8324,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8367,7 +8367,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8496,7 +8496,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8539,7 +8539,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8582,7 +8582,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8625,7 +8625,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8668,7 +8668,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8797,7 +8797,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8840,7 +8840,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8883,7 +8883,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8926,7 +8926,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9012,7 +9012,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9055,7 +9055,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>[TESTE] Gerado em: 25/09/2026 14:28 (UTC)</t>
+          <t>[TESTE] Gerado em: 26/09/2026 13:38 (UTC)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -37416,7 +37416,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -37479,7 +37479,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -37605,7 +37605,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -37731,7 +37731,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -37857,7 +37857,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -37983,7 +37983,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -38487,7 +38487,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -39180,7 +39180,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -39243,7 +39243,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -39495,7 +39495,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -39747,7 +39747,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -39999,7 +39999,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -40440,7 +40440,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -40629,7 +40629,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -40755,7 +40755,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -41070,7 +41070,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -41259,7 +41259,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -41511,7 +41511,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -41637,7 +41637,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -41763,7 +41763,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -42015,7 +42015,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -42645,7 +42645,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -42897,7 +42897,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -42960,7 +42960,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -43023,7 +43023,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -43401,7 +43401,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -43527,7 +43527,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -43653,7 +43653,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -43716,7 +43716,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -43779,7 +43779,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -43905,7 +43905,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -43968,7 +43968,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -44031,7 +44031,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -44535,7 +44535,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -44850,7 +44850,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -44913,7 +44913,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -45039,7 +45039,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -45291,7 +45291,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -45417,7 +45417,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -45543,7 +45543,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -45606,7 +45606,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -45732,7 +45732,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -45795,7 +45795,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -45984,7 +45984,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -46047,7 +46047,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -46110,7 +46110,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -46236,7 +46236,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -46362,7 +46362,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -46614,7 +46614,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -46677,7 +46677,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -46740,7 +46740,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -46803,7 +46803,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -47055,7 +47055,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -47118,7 +47118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -47244,7 +47244,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -47307,7 +47307,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -47433,7 +47433,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -47496,7 +47496,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -47559,7 +47559,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -47622,7 +47622,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -47811,7 +47811,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -47874,7 +47874,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -47937,7 +47937,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -48000,7 +48000,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -48252,7 +48252,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -48315,7 +48315,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -48378,7 +48378,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -48441,7 +48441,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -48504,7 +48504,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -48567,7 +48567,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -48630,7 +48630,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -48693,7 +48693,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -48756,7 +48756,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -48819,7 +48819,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -48945,7 +48945,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -49134,7 +49134,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -49260,7 +49260,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -49323,7 +49323,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">

--- a/mapa_classe_sondagens.xlsx
+++ b/mapa_classe_sondagens.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1272,7 +1272,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2304,7 +2304,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2648,7 +2648,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2820,7 +2820,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2863,7 +2863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2906,7 +2906,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3164,7 +3164,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3508,7 +3508,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3594,7 +3594,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4239,7 +4239,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4626,7 +4626,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4712,7 +4712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4884,7 +4884,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5357,7 +5357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5572,7 +5572,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6217,7 +6217,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6303,7 +6303,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6389,7 +6389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6432,7 +6432,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6647,7 +6647,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6690,7 +6690,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6776,7 +6776,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6905,7 +6905,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7034,7 +7034,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7335,7 +7335,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7378,7 +7378,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7507,7 +7507,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7636,7 +7636,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7722,7 +7722,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7765,7 +7765,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7851,7 +7851,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7894,7 +7894,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7937,7 +7937,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8023,7 +8023,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8066,7 +8066,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8152,7 +8152,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8238,7 +8238,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8281,7 +8281,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8324,7 +8324,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8367,7 +8367,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8496,7 +8496,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8539,7 +8539,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8582,7 +8582,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8625,7 +8625,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8668,7 +8668,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8797,7 +8797,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8840,7 +8840,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8883,7 +8883,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8926,7 +8926,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9012,7 +9012,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9055,7 +9055,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>[TESTE] Gerado em: 26/09/2026 13:38 (UTC)</t>
+          <t>[TESTE] Gerado em: 27/09/2026 14:35 (UTC)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -37416,7 +37416,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -37479,7 +37479,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -37605,7 +37605,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -37731,7 +37731,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -37857,7 +37857,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -37983,7 +37983,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -38487,7 +38487,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -39180,7 +39180,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -39243,7 +39243,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -39495,7 +39495,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -39747,7 +39747,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -39999,7 +39999,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -40440,7 +40440,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -40629,7 +40629,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -40755,7 +40755,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -41070,7 +41070,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -41259,7 +41259,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -41511,7 +41511,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -41637,7 +41637,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -41763,7 +41763,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -42015,7 +42015,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -42645,7 +42645,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -42897,7 +42897,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -42960,7 +42960,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -43023,7 +43023,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -43401,7 +43401,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -43527,7 +43527,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -43653,7 +43653,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -43716,7 +43716,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -43779,7 +43779,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -43905,7 +43905,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -43968,7 +43968,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -44031,7 +44031,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -44535,7 +44535,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -44850,7 +44850,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -44913,7 +44913,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -45039,7 +45039,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -45291,7 +45291,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -45417,7 +45417,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -45543,7 +45543,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -45606,7 +45606,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -45732,7 +45732,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -45795,7 +45795,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -45984,7 +45984,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -46047,7 +46047,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -46110,7 +46110,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -46236,7 +46236,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -46362,7 +46362,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -46614,7 +46614,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -46677,7 +46677,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -46740,7 +46740,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -46803,7 +46803,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -47055,7 +47055,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -47118,7 +47118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -47244,7 +47244,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -47307,7 +47307,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -47433,7 +47433,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -47496,7 +47496,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -47559,7 +47559,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -47622,7 +47622,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -47811,7 +47811,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -47874,7 +47874,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -47937,7 +47937,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -48000,7 +48000,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -48252,7 +48252,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -48315,7 +48315,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -48378,7 +48378,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -48441,7 +48441,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -48504,7 +48504,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -48567,7 +48567,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -48630,7 +48630,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -48693,7 +48693,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -48756,7 +48756,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -48819,7 +48819,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -48945,7 +48945,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -49134,7 +49134,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -49260,7 +49260,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -49323,7 +49323,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">

--- a/mapa_classe_sondagens.xlsx
+++ b/mapa_classe_sondagens.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1272,7 +1272,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2304,7 +2304,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2648,7 +2648,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2820,7 +2820,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2863,7 +2863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2906,7 +2906,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3164,7 +3164,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3508,7 +3508,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3594,7 +3594,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4239,7 +4239,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4626,7 +4626,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4712,7 +4712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4884,7 +4884,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5357,7 +5357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5572,7 +5572,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6217,7 +6217,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6303,7 +6303,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6389,7 +6389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6432,7 +6432,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6647,7 +6647,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6690,7 +6690,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6776,7 +6776,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6905,7 +6905,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7034,7 +7034,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7335,7 +7335,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7378,7 +7378,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7507,7 +7507,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7636,7 +7636,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7722,7 +7722,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7765,7 +7765,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7851,7 +7851,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7894,7 +7894,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7937,7 +7937,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8023,7 +8023,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8066,7 +8066,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8152,7 +8152,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8238,7 +8238,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8281,7 +8281,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8324,7 +8324,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8367,7 +8367,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8496,7 +8496,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8539,7 +8539,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8582,7 +8582,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8625,7 +8625,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8668,7 +8668,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8797,7 +8797,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8840,7 +8840,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8883,7 +8883,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8926,7 +8926,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9012,7 +9012,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9055,7 +9055,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>[TESTE] Gerado em: 27/09/2026 14:35 (UTC)</t>
+          <t>[TESTE] Gerado em: 28/09/2026 17:26 (UTC)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -37416,7 +37416,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -37479,7 +37479,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -37605,7 +37605,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -37731,7 +37731,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -37857,7 +37857,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -37983,7 +37983,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -38487,7 +38487,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -39180,7 +39180,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -39243,7 +39243,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -39495,7 +39495,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -39747,7 +39747,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -39999,7 +39999,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -40440,7 +40440,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -40629,7 +40629,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -40755,7 +40755,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -41070,7 +41070,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -41259,7 +41259,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -41511,7 +41511,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -41637,7 +41637,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -41763,7 +41763,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -42015,7 +42015,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -42645,7 +42645,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -42897,7 +42897,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -42960,7 +42960,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -43023,7 +43023,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -43401,7 +43401,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -43527,7 +43527,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -43653,7 +43653,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -43716,7 +43716,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -43779,7 +43779,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -43905,7 +43905,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -43968,7 +43968,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -44031,7 +44031,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -44535,7 +44535,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -44850,7 +44850,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -44913,7 +44913,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -45039,7 +45039,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -45291,7 +45291,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -45417,7 +45417,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -45543,7 +45543,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -45606,7 +45606,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -45732,7 +45732,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -45795,7 +45795,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -45984,7 +45984,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -46047,7 +46047,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -46110,7 +46110,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -46236,7 +46236,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -46362,7 +46362,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -46614,7 +46614,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -46677,7 +46677,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -46740,7 +46740,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -46803,7 +46803,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -47055,7 +47055,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -47118,7 +47118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -47244,7 +47244,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -47307,7 +47307,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -47433,7 +47433,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -47496,7 +47496,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -47559,7 +47559,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -47622,7 +47622,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -47811,7 +47811,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -47874,7 +47874,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -47937,7 +47937,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -48000,7 +48000,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -48252,7 +48252,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -48315,7 +48315,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -48378,7 +48378,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -48441,7 +48441,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -48504,7 +48504,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -48567,7 +48567,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -48630,7 +48630,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -48693,7 +48693,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -48756,7 +48756,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -48819,7 +48819,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -48945,7 +48945,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -49134,7 +49134,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -49260,7 +49260,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -49323,7 +49323,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">

--- a/mapa_classe_sondagens.xlsx
+++ b/mapa_classe_sondagens.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1272,7 +1272,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2304,7 +2304,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2648,7 +2648,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2820,7 +2820,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2863,7 +2863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2906,7 +2906,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3164,7 +3164,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3508,7 +3508,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3594,7 +3594,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4239,7 +4239,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4626,7 +4626,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4712,7 +4712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4884,7 +4884,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5357,7 +5357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5572,7 +5572,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6217,7 +6217,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6303,7 +6303,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6389,7 +6389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6432,7 +6432,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6647,7 +6647,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6690,7 +6690,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6776,7 +6776,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6905,7 +6905,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7034,7 +7034,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7335,7 +7335,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7378,7 +7378,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7507,7 +7507,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7636,7 +7636,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7722,7 +7722,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7765,7 +7765,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7851,7 +7851,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7894,7 +7894,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7937,7 +7937,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8023,7 +8023,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8066,7 +8066,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8152,7 +8152,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8238,7 +8238,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8281,7 +8281,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8324,7 +8324,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8367,7 +8367,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8496,7 +8496,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8539,7 +8539,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8582,7 +8582,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8625,7 +8625,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8668,7 +8668,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8797,7 +8797,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8840,7 +8840,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8883,7 +8883,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8926,7 +8926,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9012,7 +9012,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9055,7 +9055,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>[TESTE] Gerado em: 28/09/2026 17:26 (UTC)</t>
+          <t>[TESTE] Gerado em: 29/09/2026 15:26 (UTC)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -37416,7 +37416,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -37479,7 +37479,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -37605,7 +37605,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -37731,7 +37731,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -37857,7 +37857,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -37983,7 +37983,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -38487,7 +38487,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -39180,7 +39180,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -39243,7 +39243,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -39495,7 +39495,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -39747,7 +39747,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -39999,7 +39999,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -40440,7 +40440,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -40629,7 +40629,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -40755,7 +40755,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -41070,7 +41070,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -41259,7 +41259,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -41511,7 +41511,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -41637,7 +41637,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -41763,7 +41763,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -42015,7 +42015,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -42645,7 +42645,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -42897,7 +42897,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -42960,7 +42960,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -43023,7 +43023,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -43401,7 +43401,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -43527,7 +43527,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -43653,7 +43653,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -43716,7 +43716,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -43779,7 +43779,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -43905,7 +43905,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -43968,7 +43968,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -44031,7 +44031,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -44535,7 +44535,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -44850,7 +44850,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -44913,7 +44913,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -45039,7 +45039,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -45291,7 +45291,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -45417,7 +45417,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -45543,7 +45543,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -45606,7 +45606,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -45732,7 +45732,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -45795,7 +45795,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -45984,7 +45984,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -46047,7 +46047,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -46110,7 +46110,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -46236,7 +46236,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -46362,7 +46362,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -46614,7 +46614,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -46677,7 +46677,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -46740,7 +46740,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -46803,7 +46803,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -47055,7 +47055,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -47118,7 +47118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -47244,7 +47244,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -47307,7 +47307,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -47433,7 +47433,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -47496,7 +47496,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -47559,7 +47559,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -47622,7 +47622,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -47811,7 +47811,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -47874,7 +47874,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -47937,7 +47937,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -48000,7 +48000,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -48252,7 +48252,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -48315,7 +48315,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -48378,7 +48378,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -48441,7 +48441,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -48504,7 +48504,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -48567,7 +48567,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -48630,7 +48630,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -48693,7 +48693,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -48756,7 +48756,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -48819,7 +48819,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -48945,7 +48945,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -49134,7 +49134,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -49260,7 +49260,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -49323,7 +49323,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">

--- a/mapa_classe_sondagens.xlsx
+++ b/mapa_classe_sondagens.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1272,7 +1272,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2304,7 +2304,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2648,7 +2648,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2820,7 +2820,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2863,7 +2863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2906,7 +2906,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3164,7 +3164,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3508,7 +3508,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3594,7 +3594,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4239,7 +4239,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4626,7 +4626,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4712,7 +4712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4884,7 +4884,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5357,7 +5357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5572,7 +5572,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6217,7 +6217,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6303,7 +6303,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6389,7 +6389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6432,7 +6432,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6647,7 +6647,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6690,7 +6690,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6776,7 +6776,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6905,7 +6905,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7034,7 +7034,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7335,7 +7335,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7378,7 +7378,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7507,7 +7507,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7636,7 +7636,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7722,7 +7722,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7765,7 +7765,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7851,7 +7851,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7894,7 +7894,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7937,7 +7937,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8023,7 +8023,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8066,7 +8066,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8152,7 +8152,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8238,7 +8238,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8281,7 +8281,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8324,7 +8324,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8367,7 +8367,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8496,7 +8496,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8539,7 +8539,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8582,7 +8582,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8625,7 +8625,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8668,7 +8668,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8797,7 +8797,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8840,7 +8840,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8883,7 +8883,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8926,7 +8926,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9012,7 +9012,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9055,7 +9055,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>[TESTE] Gerado em: 29/09/2026 15:26 (UTC)</t>
+          <t>[TESTE] Gerado em: 30/09/2026 15:42 (UTC)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -37416,7 +37416,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -37479,7 +37479,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -37605,7 +37605,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -37731,7 +37731,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -37857,7 +37857,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -37983,7 +37983,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -38487,7 +38487,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -39180,7 +39180,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -39243,7 +39243,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -39495,7 +39495,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -39747,7 +39747,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -39999,7 +39999,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -40440,7 +40440,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -40629,7 +40629,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -40755,7 +40755,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -41070,7 +41070,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -41259,7 +41259,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -41511,7 +41511,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -41637,7 +41637,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -41763,7 +41763,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -42015,7 +42015,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -42645,7 +42645,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -42897,7 +42897,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -42960,7 +42960,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -43023,7 +43023,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -43401,7 +43401,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -43527,7 +43527,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -43653,7 +43653,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -43716,7 +43716,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -43779,7 +43779,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -43905,7 +43905,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -43968,7 +43968,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -44031,7 +44031,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -44535,7 +44535,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -44850,7 +44850,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -44913,7 +44913,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -45039,7 +45039,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -45291,7 +45291,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -45417,7 +45417,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -45543,7 +45543,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -45606,7 +45606,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -45732,7 +45732,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -45795,7 +45795,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -45984,7 +45984,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -46047,7 +46047,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -46110,7 +46110,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -46236,7 +46236,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -46362,7 +46362,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -46614,7 +46614,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -46677,7 +46677,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -46740,7 +46740,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -46803,7 +46803,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -47055,7 +47055,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -47118,7 +47118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -47244,7 +47244,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -47307,7 +47307,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -47433,7 +47433,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -47496,7 +47496,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -47559,7 +47559,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -47622,7 +47622,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -47811,7 +47811,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -47874,7 +47874,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -47937,7 +47937,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -48000,7 +48000,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -48252,7 +48252,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -48315,7 +48315,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -48378,7 +48378,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -48441,7 +48441,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -48504,7 +48504,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -48567,7 +48567,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -48630,7 +48630,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -48693,7 +48693,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -48756,7 +48756,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -48819,7 +48819,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -48945,7 +48945,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -49134,7 +49134,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -49260,7 +49260,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -49323,7 +49323,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">

--- a/mapa_classe_sondagens.xlsx
+++ b/mapa_classe_sondagens.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1272,7 +1272,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2304,7 +2304,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2648,7 +2648,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2820,7 +2820,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2863,7 +2863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2906,7 +2906,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3164,7 +3164,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3508,7 +3508,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3594,7 +3594,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4239,7 +4239,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4626,7 +4626,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4712,7 +4712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4884,7 +4884,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5357,7 +5357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5572,7 +5572,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6217,7 +6217,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6303,7 +6303,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6389,7 +6389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6432,7 +6432,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6647,7 +6647,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6690,7 +6690,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6776,7 +6776,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6905,7 +6905,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7034,7 +7034,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7335,7 +7335,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7378,7 +7378,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7507,7 +7507,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7636,7 +7636,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7722,7 +7722,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7765,7 +7765,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7851,7 +7851,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7894,7 +7894,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7937,7 +7937,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8023,7 +8023,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8066,7 +8066,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8152,7 +8152,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8238,7 +8238,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8281,7 +8281,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8324,7 +8324,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8367,7 +8367,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8496,7 +8496,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8539,7 +8539,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8582,7 +8582,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8625,7 +8625,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8668,7 +8668,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8797,7 +8797,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8840,7 +8840,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8883,7 +8883,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8926,7 +8926,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9012,7 +9012,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9055,7 +9055,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>[TESTE] Gerado em: 30/09/2026 15:42 (UTC)</t>
+          <t>[TESTE] Gerado em: 01/10/2026 16:05 (UTC)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -37416,7 +37416,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -37479,7 +37479,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -37605,7 +37605,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -37731,7 +37731,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -37857,7 +37857,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -37983,7 +37983,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -38487,7 +38487,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -39180,7 +39180,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -39243,7 +39243,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -39495,7 +39495,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -39747,7 +39747,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -39999,7 +39999,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -40440,7 +40440,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -40629,7 +40629,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -40755,7 +40755,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -41070,7 +41070,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -41259,7 +41259,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -41511,7 +41511,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -41637,7 +41637,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -41763,7 +41763,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -42015,7 +42015,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -42645,7 +42645,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -42897,7 +42897,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -42960,7 +42960,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -43023,7 +43023,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -43401,7 +43401,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -43527,7 +43527,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -43653,7 +43653,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -43716,7 +43716,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -43779,7 +43779,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -43905,7 +43905,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -43968,7 +43968,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -44031,7 +44031,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -44535,7 +44535,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -44850,7 +44850,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -44913,7 +44913,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -45039,7 +45039,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -45291,7 +45291,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -45417,7 +45417,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -45543,7 +45543,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -45606,7 +45606,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -45732,7 +45732,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -45795,7 +45795,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -45984,7 +45984,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -46047,7 +46047,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -46110,7 +46110,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -46236,7 +46236,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -46362,7 +46362,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -46614,7 +46614,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -46677,7 +46677,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -46740,7 +46740,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -46803,7 +46803,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -47055,7 +47055,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -47118,7 +47118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -47244,7 +47244,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -47307,7 +47307,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -47433,7 +47433,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -47496,7 +47496,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -47559,7 +47559,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -47622,7 +47622,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -47811,7 +47811,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -47874,7 +47874,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -47937,7 +47937,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -48000,7 +48000,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -48252,7 +48252,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -48315,7 +48315,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -48378,7 +48378,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -48441,7 +48441,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -48504,7 +48504,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -48567,7 +48567,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -48630,7 +48630,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -48693,7 +48693,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -48756,7 +48756,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -48819,7 +48819,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -48945,7 +48945,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -49134,7 +49134,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -49260,7 +49260,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -49323,7 +49323,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">

--- a/mapa_classe_sondagens.xlsx
+++ b/mapa_classe_sondagens.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1272,7 +1272,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2304,7 +2304,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2648,7 +2648,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2820,7 +2820,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2863,7 +2863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2906,7 +2906,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3164,7 +3164,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3508,7 +3508,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3594,7 +3594,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4239,7 +4239,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4626,7 +4626,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4712,7 +4712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4884,7 +4884,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5357,7 +5357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5572,7 +5572,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6217,7 +6217,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6303,7 +6303,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6389,7 +6389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6432,7 +6432,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6647,7 +6647,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6690,7 +6690,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6776,7 +6776,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6905,7 +6905,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7034,7 +7034,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7335,7 +7335,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7378,7 +7378,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7507,7 +7507,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7636,7 +7636,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7722,7 +7722,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7765,7 +7765,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7851,7 +7851,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7894,7 +7894,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7937,7 +7937,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8023,7 +8023,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8066,7 +8066,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8152,7 +8152,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8238,7 +8238,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8281,7 +8281,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8324,7 +8324,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8367,7 +8367,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8496,7 +8496,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8539,7 +8539,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8582,7 +8582,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8625,7 +8625,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8668,7 +8668,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8797,7 +8797,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8840,7 +8840,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8883,7 +8883,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8926,7 +8926,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9012,7 +9012,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9055,7 +9055,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>[TESTE] Gerado em: 01/10/2026 16:05 (UTC)</t>
+          <t>[TESTE] Gerado em: 02/10/2026 15:28 (UTC)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -37416,7 +37416,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -37479,7 +37479,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -37605,7 +37605,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -37731,7 +37731,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -37857,7 +37857,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -37983,7 +37983,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -38487,7 +38487,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -39180,7 +39180,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -39243,7 +39243,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -39495,7 +39495,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -39747,7 +39747,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -39999,7 +39999,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -40440,7 +40440,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -40629,7 +40629,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -40755,7 +40755,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -41070,7 +41070,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -41259,7 +41259,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -41511,7 +41511,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -41637,7 +41637,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -41763,7 +41763,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -42015,7 +42015,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -42645,7 +42645,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -42897,7 +42897,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -42960,7 +42960,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -43023,7 +43023,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -43401,7 +43401,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -43527,7 +43527,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -43653,7 +43653,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -43716,7 +43716,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -43779,7 +43779,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -43905,7 +43905,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -43968,7 +43968,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -44031,7 +44031,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -44535,7 +44535,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -44850,7 +44850,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -44913,7 +44913,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -45039,7 +45039,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -45291,7 +45291,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -45417,7 +45417,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -45543,7 +45543,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -45606,7 +45606,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -45732,7 +45732,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -45795,7 +45795,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -45984,7 +45984,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -46047,7 +46047,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -46110,7 +46110,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -46236,7 +46236,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -46362,7 +46362,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -46614,7 +46614,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -46677,7 +46677,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -46740,7 +46740,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -46803,7 +46803,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -47055,7 +47055,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -47118,7 +47118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -47244,7 +47244,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -47307,7 +47307,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -47433,7 +47433,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -47496,7 +47496,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -47559,7 +47559,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -47622,7 +47622,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -47811,7 +47811,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -47874,7 +47874,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -47937,7 +47937,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -48000,7 +48000,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -48252,7 +48252,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -48315,7 +48315,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -48378,7 +48378,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -48441,7 +48441,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -48504,7 +48504,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -48567,7 +48567,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -48630,7 +48630,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -48693,7 +48693,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -48756,7 +48756,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -48819,7 +48819,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -48945,7 +48945,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -49134,7 +49134,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -49260,7 +49260,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -49323,7 +49323,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">

--- a/mapa_classe_sondagens.xlsx
+++ b/mapa_classe_sondagens.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1272,7 +1272,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2304,7 +2304,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2648,7 +2648,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2820,7 +2820,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2863,7 +2863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2906,7 +2906,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3164,7 +3164,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3508,7 +3508,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3594,7 +3594,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4239,7 +4239,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4626,7 +4626,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4712,7 +4712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4884,7 +4884,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5357,7 +5357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5572,7 +5572,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6217,7 +6217,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6303,7 +6303,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6389,7 +6389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6432,7 +6432,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6647,7 +6647,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6690,7 +6690,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6776,7 +6776,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6905,7 +6905,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7034,7 +7034,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7335,7 +7335,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7378,7 +7378,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7507,7 +7507,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7636,7 +7636,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7722,7 +7722,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7765,7 +7765,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7851,7 +7851,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7894,7 +7894,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7937,7 +7937,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8023,7 +8023,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8066,7 +8066,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8152,7 +8152,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8238,7 +8238,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8281,7 +8281,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8324,7 +8324,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8367,7 +8367,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8496,7 +8496,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8539,7 +8539,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8582,7 +8582,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8625,7 +8625,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8668,7 +8668,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8797,7 +8797,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8840,7 +8840,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8883,7 +8883,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8926,7 +8926,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9012,7 +9012,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9055,7 +9055,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>[TESTE] Gerado em: 02/10/2026 15:28 (UTC)</t>
+          <t>[TESTE] Gerado em: 03/10/2026 14:10 (UTC)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -37416,7 +37416,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -37479,7 +37479,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -37605,7 +37605,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -37731,7 +37731,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -37857,7 +37857,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -37983,7 +37983,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -38487,7 +38487,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -39180,7 +39180,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -39243,7 +39243,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -39495,7 +39495,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -39747,7 +39747,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -39999,7 +39999,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -40440,7 +40440,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -40629,7 +40629,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -40755,7 +40755,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -41070,7 +41070,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -41259,7 +41259,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -41511,7 +41511,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -41637,7 +41637,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -41763,7 +41763,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -42015,7 +42015,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -42645,7 +42645,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -42897,7 +42897,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -42960,7 +42960,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -43023,7 +43023,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -43401,7 +43401,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -43527,7 +43527,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -43653,7 +43653,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -43716,7 +43716,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -43779,7 +43779,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -43905,7 +43905,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -43968,7 +43968,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -44031,7 +44031,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -44535,7 +44535,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -44850,7 +44850,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -44913,7 +44913,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -45039,7 +45039,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -45291,7 +45291,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -45417,7 +45417,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -45543,7 +45543,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -45606,7 +45606,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -45732,7 +45732,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -45795,7 +45795,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -45984,7 +45984,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -46047,7 +46047,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -46110,7 +46110,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -46236,7 +46236,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -46362,7 +46362,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -46614,7 +46614,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -46677,7 +46677,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -46740,7 +46740,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -46803,7 +46803,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -47055,7 +47055,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -47118,7 +47118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -47244,7 +47244,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -47307,7 +47307,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -47433,7 +47433,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -47496,7 +47496,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -47559,7 +47559,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -47622,7 +47622,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -47811,7 +47811,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -47874,7 +47874,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -47937,7 +47937,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -48000,7 +48000,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -48252,7 +48252,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -48315,7 +48315,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -48378,7 +48378,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -48441,7 +48441,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -48504,7 +48504,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -48567,7 +48567,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -48630,7 +48630,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -48693,7 +48693,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -48756,7 +48756,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -48819,7 +48819,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -48945,7 +48945,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -49134,7 +49134,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -49260,7 +49260,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -49323,7 +49323,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">

--- a/mapa_classe_sondagens.xlsx
+++ b/mapa_classe_sondagens.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1272,7 +1272,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2304,7 +2304,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2648,7 +2648,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2820,7 +2820,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2863,7 +2863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2906,7 +2906,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3164,7 +3164,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3508,7 +3508,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3594,7 +3594,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4239,7 +4239,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4626,7 +4626,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4712,7 +4712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4884,7 +4884,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5357,7 +5357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5572,7 +5572,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6217,7 +6217,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6303,7 +6303,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6389,7 +6389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6432,7 +6432,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6647,7 +6647,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6690,7 +6690,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6776,7 +6776,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6905,7 +6905,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7034,7 +7034,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7335,7 +7335,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7378,7 +7378,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7507,7 +7507,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7636,7 +7636,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7722,7 +7722,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7765,7 +7765,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7851,7 +7851,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7894,7 +7894,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7937,7 +7937,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8023,7 +8023,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8066,7 +8066,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8152,7 +8152,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8238,7 +8238,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8281,7 +8281,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8324,7 +8324,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8367,7 +8367,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8496,7 +8496,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8539,7 +8539,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8582,7 +8582,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8625,7 +8625,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8668,7 +8668,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8797,7 +8797,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8840,7 +8840,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8883,7 +8883,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8926,7 +8926,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9012,7 +9012,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9055,7 +9055,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>[TESTE] Gerado em: 03/10/2026 14:10 (UTC)</t>
+          <t>[TESTE] Gerado em: 04/10/2026 14:40 (UTC)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -37416,7 +37416,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -37479,7 +37479,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -37605,7 +37605,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -37731,7 +37731,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -37857,7 +37857,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -37983,7 +37983,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -38487,7 +38487,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -39180,7 +39180,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -39243,7 +39243,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -39495,7 +39495,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -39747,7 +39747,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -39999,7 +39999,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -40440,7 +40440,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -40629,7 +40629,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -40755,7 +40755,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -41070,7 +41070,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -41259,7 +41259,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -41511,7 +41511,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -41637,7 +41637,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -41763,7 +41763,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -42015,7 +42015,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -42645,7 +42645,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -42897,7 +42897,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -42960,7 +42960,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -43023,7 +43023,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -43401,7 +43401,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -43527,7 +43527,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -43653,7 +43653,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -43716,7 +43716,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -43779,7 +43779,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -43905,7 +43905,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -43968,7 +43968,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -44031,7 +44031,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -44535,7 +44535,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -44850,7 +44850,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -44913,7 +44913,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -45039,7 +45039,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -45291,7 +45291,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -45417,7 +45417,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -45543,7 +45543,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -45606,7 +45606,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -45732,7 +45732,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -45795,7 +45795,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -45984,7 +45984,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -46047,7 +46047,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -46110,7 +46110,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -46236,7 +46236,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -46362,7 +46362,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -46614,7 +46614,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -46677,7 +46677,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -46740,7 +46740,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -46803,7 +46803,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -47055,7 +47055,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -47118,7 +47118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -47244,7 +47244,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -47307,7 +47307,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -47433,7 +47433,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -47496,7 +47496,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -47559,7 +47559,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -47622,7 +47622,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -47811,7 +47811,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -47874,7 +47874,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -47937,7 +47937,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -48000,7 +48000,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -48252,7 +48252,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -48315,7 +48315,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -48378,7 +48378,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -48441,7 +48441,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -48504,7 +48504,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -48567,7 +48567,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -48630,7 +48630,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -48693,7 +48693,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -48756,7 +48756,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -48819,7 +48819,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -48945,7 +48945,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -49134,7 +49134,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -49260,7 +49260,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -49323,7 +49323,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">

--- a/mapa_classe_sondagens.xlsx
+++ b/mapa_classe_sondagens.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1272,7 +1272,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2304,7 +2304,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2648,7 +2648,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2820,7 +2820,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2863,7 +2863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2906,7 +2906,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3164,7 +3164,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3508,7 +3508,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3594,7 +3594,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4239,7 +4239,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4626,7 +4626,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4712,7 +4712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4884,7 +4884,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5357,7 +5357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5572,7 +5572,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6217,7 +6217,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6303,7 +6303,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6389,7 +6389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6432,7 +6432,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6647,7 +6647,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6690,7 +6690,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6776,7 +6776,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6905,7 +6905,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7034,7 +7034,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7335,7 +7335,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7378,7 +7378,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7507,7 +7507,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7636,7 +7636,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7722,7 +7722,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7765,7 +7765,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7851,7 +7851,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7894,7 +7894,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7937,7 +7937,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8023,7 +8023,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8066,7 +8066,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8152,7 +8152,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8238,7 +8238,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8281,7 +8281,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8324,7 +8324,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8367,7 +8367,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8496,7 +8496,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8539,7 +8539,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8582,7 +8582,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8625,7 +8625,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8668,7 +8668,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8797,7 +8797,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8840,7 +8840,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8883,7 +8883,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8926,7 +8926,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9012,7 +9012,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9055,7 +9055,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>[TESTE] Gerado em: 04/10/2026 14:40 (UTC)</t>
+          <t>[TESTE] Gerado em: 05/10/2026 18:03 (UTC)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -37416,7 +37416,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -37479,7 +37479,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -37605,7 +37605,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -37731,7 +37731,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -37857,7 +37857,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -37983,7 +37983,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -38487,7 +38487,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -39180,7 +39180,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -39243,7 +39243,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -39495,7 +39495,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -39747,7 +39747,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -39999,7 +39999,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -40440,7 +40440,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -40629,7 +40629,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -40755,7 +40755,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -41070,7 +41070,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -41259,7 +41259,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -41511,7 +41511,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -41637,7 +41637,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -41763,7 +41763,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -42015,7 +42015,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -42645,7 +42645,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -42897,7 +42897,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -42960,7 +42960,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -43023,7 +43023,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -43401,7 +43401,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -43527,7 +43527,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -43653,7 +43653,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -43716,7 +43716,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -43779,7 +43779,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -43905,7 +43905,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -43968,7 +43968,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -44031,7 +44031,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -44535,7 +44535,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -44850,7 +44850,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -44913,7 +44913,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -45039,7 +45039,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -45291,7 +45291,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -45417,7 +45417,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -45543,7 +45543,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -45606,7 +45606,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -45732,7 +45732,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -45795,7 +45795,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -45984,7 +45984,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -46047,7 +46047,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -46110,7 +46110,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -46236,7 +46236,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -46362,7 +46362,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -46614,7 +46614,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -46677,7 +46677,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -46740,7 +46740,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -46803,7 +46803,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -47055,7 +47055,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -47118,7 +47118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -47244,7 +47244,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -47307,7 +47307,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -47433,7 +47433,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -47496,7 +47496,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -47559,7 +47559,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -47622,7 +47622,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -47811,7 +47811,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -47874,7 +47874,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -47937,7 +47937,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -48000,7 +48000,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -48252,7 +48252,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -48315,7 +48315,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -48378,7 +48378,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -48441,7 +48441,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -48504,7 +48504,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -48567,7 +48567,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -48630,7 +48630,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -48693,7 +48693,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -48756,7 +48756,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -48819,7 +48819,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -48945,7 +48945,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -49134,7 +49134,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -49260,7 +49260,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -49323,7 +49323,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">

--- a/mapa_classe_sondagens.xlsx
+++ b/mapa_classe_sondagens.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1272,7 +1272,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2304,7 +2304,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2648,7 +2648,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2820,7 +2820,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2863,7 +2863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2906,7 +2906,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3164,7 +3164,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3508,7 +3508,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3594,7 +3594,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4239,7 +4239,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4626,7 +4626,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4712,7 +4712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4884,7 +4884,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5357,7 +5357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5572,7 +5572,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6217,7 +6217,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6303,7 +6303,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6389,7 +6389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6432,7 +6432,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6647,7 +6647,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6690,7 +6690,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6776,7 +6776,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6905,7 +6905,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7034,7 +7034,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7335,7 +7335,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7378,7 +7378,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7507,7 +7507,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7636,7 +7636,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7722,7 +7722,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7765,7 +7765,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7851,7 +7851,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7894,7 +7894,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7937,7 +7937,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8023,7 +8023,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8066,7 +8066,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8152,7 +8152,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8238,7 +8238,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8281,7 +8281,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8324,7 +8324,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8367,7 +8367,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8496,7 +8496,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8539,7 +8539,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8582,7 +8582,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8625,7 +8625,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8668,7 +8668,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8797,7 +8797,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8840,7 +8840,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8883,7 +8883,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8926,7 +8926,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9012,7 +9012,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9055,7 +9055,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>[TESTE] Gerado em: 05/10/2026 18:03 (UTC)</t>
+          <t>[TESTE] Gerado em: 06/10/2026 15:44 (UTC)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -37416,7 +37416,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -37479,7 +37479,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -37605,7 +37605,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -37731,7 +37731,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -37857,7 +37857,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -37983,7 +37983,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -38487,7 +38487,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -39180,7 +39180,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -39243,7 +39243,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -39495,7 +39495,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -39747,7 +39747,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -39999,7 +39999,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -40377,7 +40377,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -40440,7 +40440,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -40629,7 +40629,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -40755,7 +40755,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -41070,7 +41070,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -41259,7 +41259,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -41511,7 +41511,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -41637,7 +41637,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -41763,7 +41763,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -42015,7 +42015,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -42645,7 +42645,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -42897,7 +42897,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -42960,7 +42960,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -43023,7 +43023,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -43401,7 +43401,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -43527,7 +43527,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -43653,7 +43653,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -43716,7 +43716,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -43779,7 +43779,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -43905,7 +43905,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -43968,7 +43968,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -44031,7 +44031,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -44535,7 +44535,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -44850,7 +44850,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -44913,7 +44913,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -45039,7 +45039,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -45291,7 +45291,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -45417,7 +45417,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -45543,7 +45543,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -45606,7 +45606,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -45732,7 +45732,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -45795,7 +45795,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -45984,7 +45984,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -46047,7 +46047,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -46110,7 +46110,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -46236,7 +46236,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -46362,7 +46362,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -46614,7 +46614,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -46677,7 +46677,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -46740,7 +46740,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -46803,7 +46803,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -47055,7 +47055,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -47118,7 +47118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -47244,7 +47244,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -47307,7 +47307,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -47433,7 +47433,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -47496,7 +47496,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -47559,7 +47559,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -47622,7 +47622,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -47811,7 +47811,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -47874,7 +47874,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -47937,7 +47937,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -48000,7 +48000,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -48252,7 +48252,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -48315,7 +48315,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -48378,7 +48378,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -48441,7 +48441,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -48504,7 +48504,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -48567,7 +48567,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -48630,7 +48630,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -48693,7 +48693,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -48756,7 +48756,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -48819,7 +48819,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -48945,7 +48945,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -49134,7 +49134,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -49260,7 +49260,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -49323,7 +49323,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">

--- a/mapa_classe_sondagens.xlsx
+++ b/mapa_classe_sondagens.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1272,7 +1272,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2304,7 +2304,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2648,7 +2648,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2820,7 +2820,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2863,7 +2863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2906,7 +2906,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3164,7 +3164,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3508,7 +3508,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3594,7 +3594,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3852,7 +3852,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4239,7 +4239,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4540,7 +4540,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4626,7 +4626,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4712,7 +4712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4884,7 +4884,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5357,7 +5357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5572,7 +5572,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6217,7 +6217,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6303,7 +6303,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6389,7 +6389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6432,7 +6432,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6647,7 +6647,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6690,7 +6690,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6776,7 +6776,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6905,7 +6905,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7034,7 +7034,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7206,7 +7206,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7335,7 +7335,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7378,7 +7378,7 @@
     <